--- a/data/test.xlsx
+++ b/data/test.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
   <si>
     <t>Metal</t>
   </si>
@@ -69,6 +69,9 @@
   </si>
   <si>
     <t>acac</t>
+  </si>
+  <si>
+    <t>Cu</t>
   </si>
 </sst>
 </file>
@@ -96,11 +99,9 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
+      <sz val="14"/>
+      <name val="Arial"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -247,7 +248,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -256,6 +257,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -388,12 +401,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -441,7 +448,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -461,6 +468,21 @@
       </top>
       <bottom style="thin">
         <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
       </bottom>
       <diagonal/>
     </border>
@@ -567,19 +589,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -588,7 +610,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -600,125 +622,131 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1039,8 +1067,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="1"/>
+  <dimension ref="A1:L3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="2"/>
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="2" t="s">
@@ -1111,6 +1139,39 @@
       <c r="J2" s="1">
         <v>0</v>
       </c>
+    </row>
+    <row r="3" ht="20.4" spans="1:12">
+      <c r="A3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="3">
+        <v>3.44</v>
+      </c>
+      <c r="D3" s="3">
+        <v>2</v>
+      </c>
+      <c r="E3" s="3">
+        <v>3.509</v>
+      </c>
+      <c r="F3" s="3">
+        <v>1</v>
+      </c>
+      <c r="G3" s="3">
+        <v>1.9</v>
+      </c>
+      <c r="H3" s="3">
+        <v>0.57</v>
+      </c>
+      <c r="I3" s="3">
+        <v>0</v>
+      </c>
+      <c r="J3" s="3">
+        <v>9</v>
+      </c>
+      <c r="K3" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
